--- a/intermediarios-nao-mexer.xlsx
+++ b/intermediarios-nao-mexer.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Matheus\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projeto-banco de dados\formularios-contas-alphas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F4B172F-BA55-43D5-8D74-4F70D8D1966F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FF8CB5E-1EB5-41C7-907B-631B543AC7A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="5" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="00_README" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2027" uniqueCount="464">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2136" uniqueCount="467">
   <si>
     <t>Modelo Excel (Intermediários) para análise e dashboard, preservando tudo.</t>
   </si>
@@ -1433,6 +1433,15 @@
   </si>
   <si>
     <t>Brasilia, Fabio, Laranjal do Jari; Obidos - Caiba; Belém -Mutram; Monte Dourado - Garcilazio;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">José Alves Leitão </t>
+  </si>
+  <si>
+    <t>Alenquer</t>
+  </si>
+  <si>
+    <t>Cacau</t>
   </si>
 </sst>
 </file>
@@ -1521,8 +1530,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="T_DIM_Comprador" displayName="T_DIM_Comprador" ref="A1:B35">
-  <autoFilter ref="A1:B35" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="T_DIM_Comprador" displayName="T_DIM_Comprador" ref="A1:B36">
+  <autoFilter ref="A1:B36" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="id_comprador"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="comprador"/>
@@ -1532,8 +1541,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="T_FACT_Compras_2_3" displayName="T_FACT_Compras_2_3" ref="A1:Z154">
-  <autoFilter ref="A1:Z154" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="T_FACT_Compras_2_3" displayName="T_FACT_Compras_2_3" ref="A1:Z157">
+  <autoFilter ref="A1:Z157" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
   <tableColumns count="26">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="id_intermediario"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Nº do questionário"/>
@@ -1567,8 +1576,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="T_FACT_Vendas_4" displayName="T_FACT_Vendas_4" ref="A1:Z50">
-  <autoFilter ref="A1:Z50" xr:uid="{00000000-0009-0000-0100-000006000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="T_FACT_Vendas_4" displayName="T_FACT_Vendas_4" ref="A1:Z53">
+  <autoFilter ref="A1:Z53" xr:uid="{00000000-0009-0000-0100-000006000000}"/>
   <tableColumns count="26">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="id_intermediario"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="Nº do questionário"/>
@@ -1602,8 +1611,8 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="T_BRIDGE_Comunidades_Compra" displayName="T_BRIDGE_Comunidades_Compra" ref="A1:E163">
-  <autoFilter ref="A1:E163" xr:uid="{00000000-0009-0000-0100-000007000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="T_BRIDGE_Comunidades_Compra" displayName="T_BRIDGE_Comunidades_Compra" ref="A1:E168">
+  <autoFilter ref="A1:E168" xr:uid="{00000000-0009-0000-0100-000007000000}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" name="id_intermediario"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" name="Nº do questionário"/>
@@ -1616,8 +1625,8 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{00000000-000C-0000-FFFF-FFFF07000000}" name="T_BRIDGE_Compradores_Venda" displayName="T_BRIDGE_Compradores_Venda" ref="A1:E53">
-  <autoFilter ref="A1:E53" xr:uid="{00000000-0009-0000-0100-000008000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{00000000-000C-0000-FFFF-FFFF07000000}" name="T_BRIDGE_Compradores_Venda" displayName="T_BRIDGE_Compradores_Venda" ref="A1:E56">
+  <autoFilter ref="A1:E56" xr:uid="{00000000-0009-0000-0100-000008000000}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0700-000001000000}" name="id_intermediario"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0700-000002000000}" name="Nº do questionário"/>
@@ -1915,37 +1924,37 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="120" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -1958,12 +1967,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>422</v>
       </c>
@@ -1971,7 +1980,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1979,7 +1988,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1987,7 +1996,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1995,7 +2004,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2003,7 +2012,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2011,7 +2020,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2019,7 +2028,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2027,7 +2036,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2035,7 +2044,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2043,7 +2052,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2051,7 +2060,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2070,13 +2079,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:B16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="38.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>424</v>
       </c>
@@ -2084,7 +2093,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2092,7 +2101,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2100,7 +2109,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2108,7 +2117,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2116,7 +2125,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2124,7 +2133,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2132,7 +2141,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2140,7 +2149,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2148,7 +2157,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2156,7 +2165,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2164,7 +2173,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2172,7 +2181,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2180,7 +2189,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2188,7 +2197,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2196,7 +2205,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2215,13 +2224,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:B107"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="150.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="150.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>426</v>
       </c>
@@ -2229,7 +2238,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2237,7 +2246,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2245,7 +2254,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2253,7 +2262,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2261,7 +2270,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2269,7 +2278,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2277,7 +2286,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2285,7 +2294,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2293,7 +2302,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2301,7 +2310,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2309,7 +2318,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2317,7 +2326,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2325,7 +2334,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2333,7 +2342,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2341,7 +2350,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2349,7 +2358,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -2357,7 +2366,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -2365,7 +2374,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -2373,7 +2382,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
@@ -2381,7 +2390,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
@@ -2389,7 +2398,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
@@ -2397,7 +2406,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
@@ -2405,7 +2414,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
@@ -2413,7 +2422,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
@@ -2421,7 +2430,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
@@ -2429,7 +2438,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
@@ -2437,7 +2446,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
@@ -2445,7 +2454,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
@@ -2453,7 +2462,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
@@ -2461,7 +2470,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>30</v>
       </c>
@@ -2469,7 +2478,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>31</v>
       </c>
@@ -2477,7 +2486,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>32</v>
       </c>
@@ -2485,7 +2494,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>33</v>
       </c>
@@ -2493,7 +2502,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>34</v>
       </c>
@@ -2501,7 +2510,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>35</v>
       </c>
@@ -2509,7 +2518,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>36</v>
       </c>
@@ -2517,7 +2526,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>37</v>
       </c>
@@ -2525,7 +2534,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>38</v>
       </c>
@@ -2533,7 +2542,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>39</v>
       </c>
@@ -2541,7 +2550,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>40</v>
       </c>
@@ -2549,7 +2558,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>41</v>
       </c>
@@ -2557,7 +2566,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>42</v>
       </c>
@@ -2565,7 +2574,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>43</v>
       </c>
@@ -2573,7 +2582,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>44</v>
       </c>
@@ -2581,7 +2590,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>45</v>
       </c>
@@ -2589,7 +2598,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>46</v>
       </c>
@@ -2597,7 +2606,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>47</v>
       </c>
@@ -2605,7 +2614,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>48</v>
       </c>
@@ -2613,7 +2622,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>49</v>
       </c>
@@ -2621,7 +2630,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>50</v>
       </c>
@@ -2629,7 +2638,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>51</v>
       </c>
@@ -2637,7 +2646,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>52</v>
       </c>
@@ -2645,7 +2654,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>53</v>
       </c>
@@ -2653,7 +2662,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>54</v>
       </c>
@@ -2661,7 +2670,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>55</v>
       </c>
@@ -2669,7 +2678,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>56</v>
       </c>
@@ -2677,7 +2686,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>57</v>
       </c>
@@ -2685,7 +2694,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>58</v>
       </c>
@@ -2693,7 +2702,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>59</v>
       </c>
@@ -2701,7 +2710,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>60</v>
       </c>
@@ -2709,7 +2718,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>61</v>
       </c>
@@ -2717,7 +2726,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>62</v>
       </c>
@@ -2725,7 +2734,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>63</v>
       </c>
@@ -2733,7 +2742,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>64</v>
       </c>
@@ -2741,7 +2750,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>65</v>
       </c>
@@ -2749,7 +2758,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>66</v>
       </c>
@@ -2757,7 +2766,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>67</v>
       </c>
@@ -2765,7 +2774,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>68</v>
       </c>
@@ -2773,7 +2782,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>69</v>
       </c>
@@ -2781,7 +2790,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>70</v>
       </c>
@@ -2789,7 +2798,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>71</v>
       </c>
@@ -2797,7 +2806,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>72</v>
       </c>
@@ -2805,7 +2814,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>73</v>
       </c>
@@ -2813,7 +2822,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>74</v>
       </c>
@@ -2821,7 +2830,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>75</v>
       </c>
@@ -2829,7 +2838,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>76</v>
       </c>
@@ -2837,7 +2846,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>77</v>
       </c>
@@ -2845,7 +2854,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>78</v>
       </c>
@@ -2853,7 +2862,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>79</v>
       </c>
@@ -2861,7 +2870,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>80</v>
       </c>
@@ -2869,7 +2878,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>81</v>
       </c>
@@ -2877,7 +2886,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>82</v>
       </c>
@@ -2885,7 +2894,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>83</v>
       </c>
@@ -2893,7 +2902,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>84</v>
       </c>
@@ -2901,7 +2910,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>85</v>
       </c>
@@ -2909,7 +2918,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>86</v>
       </c>
@@ -2917,7 +2926,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>87</v>
       </c>
@@ -2925,7 +2934,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>88</v>
       </c>
@@ -2933,7 +2942,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>89</v>
       </c>
@@ -2941,7 +2950,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>90</v>
       </c>
@@ -2949,7 +2958,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>91</v>
       </c>
@@ -2957,7 +2966,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>92</v>
       </c>
@@ -2965,7 +2974,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>93</v>
       </c>
@@ -2973,7 +2982,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>94</v>
       </c>
@@ -2981,7 +2990,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>95</v>
       </c>
@@ -2989,7 +2998,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>96</v>
       </c>
@@ -2997,7 +3006,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>97</v>
       </c>
@@ -3005,7 +3014,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>98</v>
       </c>
@@ -3013,7 +3022,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>99</v>
       </c>
@@ -3021,7 +3030,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>100</v>
       </c>
@@ -3029,7 +3038,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>101</v>
       </c>
@@ -3037,7 +3046,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>102</v>
       </c>
@@ -3045,7 +3054,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>103</v>
       </c>
@@ -3053,7 +3062,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>104</v>
       </c>
@@ -3061,7 +3070,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>105</v>
       </c>
@@ -3069,7 +3078,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>106</v>
       </c>
@@ -3087,14 +3096,14 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
-  <dimension ref="A1:B35"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B36"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.140625" customWidth="1"/>
-    <col min="2" max="2" width="39.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.109375" customWidth="1"/>
+    <col min="2" max="2" width="39.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>438</v>
       </c>
@@ -3102,7 +3111,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -3110,7 +3119,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -3118,7 +3127,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -3126,7 +3135,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -3134,7 +3143,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -3142,7 +3151,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -3150,7 +3159,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -3158,7 +3167,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -3166,7 +3175,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -3174,7 +3183,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -3182,7 +3191,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -3190,7 +3199,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -3198,7 +3207,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -3206,7 +3215,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -3214,7 +3223,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -3222,7 +3231,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -3230,7 +3239,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -3238,7 +3247,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -3246,7 +3255,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
@@ -3254,7 +3263,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
@@ -3262,7 +3271,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
@@ -3270,7 +3279,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
@@ -3278,7 +3287,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
@@ -3286,7 +3295,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
@@ -3294,7 +3303,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
@@ -3302,7 +3311,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
@@ -3310,7 +3319,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
@@ -3318,7 +3327,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
@@ -3326,7 +3335,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
@@ -3334,7 +3343,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>30</v>
       </c>
@@ -3342,7 +3351,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>31</v>
       </c>
@@ -3350,7 +3359,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>32</v>
       </c>
@@ -3358,7 +3367,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>33</v>
       </c>
@@ -3366,12 +3375,20 @@
         <v>406</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>34</v>
       </c>
       <c r="B35" t="s">
         <v>378</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
+        <v>464</v>
       </c>
     </row>
   </sheetData>
@@ -3384,38 +3401,38 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
-  <dimension ref="A1:Z154"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:Z156"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="150.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="24.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="21.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="33.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="28.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="37.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="150.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="33.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="28.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="37.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.44140625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="45" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="45.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="45.44140625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="12" customWidth="1"/>
-    <col min="16" max="16" width="20.42578125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="34.7109375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="44.85546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="45.28515625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="34.6640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="44.88671875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="45.33203125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="20.5546875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="20.88671875" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="47" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="151.85546875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="151.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>446</v>
       </c>
@@ -3495,7 +3512,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>51</v>
       </c>
@@ -3557,7 +3574,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>51</v>
       </c>
@@ -3619,7 +3636,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>52</v>
       </c>
@@ -3681,7 +3698,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>52</v>
       </c>
@@ -3734,7 +3751,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>53</v>
       </c>
@@ -3796,7 +3813,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>53</v>
       </c>
@@ -3861,7 +3878,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>53</v>
       </c>
@@ -3923,7 +3940,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>53</v>
       </c>
@@ -3988,7 +4005,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>53</v>
       </c>
@@ -4053,7 +4070,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>53</v>
       </c>
@@ -4133,7 +4150,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>53</v>
       </c>
@@ -4192,7 +4209,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>53</v>
       </c>
@@ -4251,7 +4268,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>54</v>
       </c>
@@ -4316,7 +4333,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>54</v>
       </c>
@@ -4387,7 +4404,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>55</v>
       </c>
@@ -4449,7 +4466,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="17" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>55</v>
       </c>
@@ -4511,7 +4528,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="18" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>55</v>
       </c>
@@ -4573,7 +4590,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="19" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>55</v>
       </c>
@@ -4635,7 +4652,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="20" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>55</v>
       </c>
@@ -4697,7 +4714,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="21" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>55</v>
       </c>
@@ -4759,7 +4776,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="22" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>55</v>
       </c>
@@ -4821,7 +4838,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="23" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>55</v>
       </c>
@@ -4883,7 +4900,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="24" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>55</v>
       </c>
@@ -4945,7 +4962,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="25" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>55</v>
       </c>
@@ -5007,7 +5024,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="26" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>55</v>
       </c>
@@ -5072,7 +5089,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="27" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>55</v>
       </c>
@@ -5134,7 +5151,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="28" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>55</v>
       </c>
@@ -5196,7 +5213,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="29" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>55</v>
       </c>
@@ -5258,7 +5275,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="30" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>55</v>
       </c>
@@ -5320,7 +5337,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="31" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>55</v>
       </c>
@@ -5382,7 +5399,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="32" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>55</v>
       </c>
@@ -5444,7 +5461,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="33" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>55</v>
       </c>
@@ -5506,7 +5523,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="34" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>55</v>
       </c>
@@ -5568,7 +5585,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="35" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>55</v>
       </c>
@@ -5630,7 +5647,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="36" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>55</v>
       </c>
@@ -5692,7 +5709,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="37" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>55</v>
       </c>
@@ -5754,7 +5771,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="38" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>55</v>
       </c>
@@ -5816,7 +5833,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="39" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>55</v>
       </c>
@@ -5878,7 +5895,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="40" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>55</v>
       </c>
@@ -5940,7 +5957,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="41" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>55</v>
       </c>
@@ -6002,7 +6019,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="42" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>55</v>
       </c>
@@ -6064,7 +6081,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="43" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>55</v>
       </c>
@@ -6126,7 +6143,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="44" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>55</v>
       </c>
@@ -6188,7 +6205,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="45" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>55</v>
       </c>
@@ -6250,7 +6267,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="46" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>55</v>
       </c>
@@ -6312,7 +6329,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="47" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>55</v>
       </c>
@@ -6374,7 +6391,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="48" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>55</v>
       </c>
@@ -6436,7 +6453,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="49" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>55</v>
       </c>
@@ -6498,7 +6515,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="50" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>55</v>
       </c>
@@ -6560,7 +6577,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="51" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>56</v>
       </c>
@@ -6616,7 +6633,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="52" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>56</v>
       </c>
@@ -6675,7 +6692,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="53" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>56</v>
       </c>
@@ -6734,7 +6751,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="54" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>56</v>
       </c>
@@ -6793,7 +6810,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="55" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>56</v>
       </c>
@@ -6852,7 +6869,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="56" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>56</v>
       </c>
@@ -6905,7 +6922,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="57" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>56</v>
       </c>
@@ -6964,7 +6981,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="58" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>56</v>
       </c>
@@ -7023,7 +7040,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="59" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>56</v>
       </c>
@@ -7082,7 +7099,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="60" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>56</v>
       </c>
@@ -7135,7 +7152,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="61" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>56</v>
       </c>
@@ -7194,7 +7211,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="62" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>56</v>
       </c>
@@ -7253,7 +7270,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="63" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>56</v>
       </c>
@@ -7312,7 +7329,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="64" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>56</v>
       </c>
@@ -7371,7 +7388,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="65" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>56</v>
       </c>
@@ -7430,7 +7447,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="66" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>56</v>
       </c>
@@ -7489,7 +7506,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="67" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>56</v>
       </c>
@@ -7548,7 +7565,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="68" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>56</v>
       </c>
@@ -7607,7 +7624,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="69" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>56</v>
       </c>
@@ -7672,7 +7689,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="70" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>56</v>
       </c>
@@ -7752,7 +7769,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="71" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>56</v>
       </c>
@@ -7817,7 +7834,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="72" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>56</v>
       </c>
@@ -7870,7 +7887,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="73" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>56</v>
       </c>
@@ -7935,7 +7952,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="74" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>56</v>
       </c>
@@ -7988,7 +8005,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="75" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>56</v>
       </c>
@@ -8047,7 +8064,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="76" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>56</v>
       </c>
@@ -8112,7 +8129,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="77" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>57</v>
       </c>
@@ -8171,7 +8188,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="78" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>57</v>
       </c>
@@ -8230,7 +8247,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="79" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>57</v>
       </c>
@@ -8289,7 +8306,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="80" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>57</v>
       </c>
@@ -8348,7 +8365,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="81" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>57</v>
       </c>
@@ -8404,7 +8421,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="82" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>58</v>
       </c>
@@ -8457,7 +8474,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="83" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>58</v>
       </c>
@@ -8522,7 +8539,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="84" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>58</v>
       </c>
@@ -8581,7 +8598,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="85" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>59</v>
       </c>
@@ -8640,7 +8657,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="86" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>59</v>
       </c>
@@ -8699,7 +8716,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="87" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>59</v>
       </c>
@@ -8758,7 +8775,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="88" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>59</v>
       </c>
@@ -8817,7 +8834,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="89" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>59</v>
       </c>
@@ -8876,7 +8893,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="90" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>59</v>
       </c>
@@ -8935,7 +8952,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="91" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>59</v>
       </c>
@@ -8994,7 +9011,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="92" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>59</v>
       </c>
@@ -9053,7 +9070,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="93" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>59</v>
       </c>
@@ -9112,7 +9129,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="94" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>59</v>
       </c>
@@ -9171,7 +9188,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="95" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>59</v>
       </c>
@@ -9230,7 +9247,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="96" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>59</v>
       </c>
@@ -9289,7 +9306,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="97" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>59</v>
       </c>
@@ -9348,7 +9365,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="98" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>59</v>
       </c>
@@ -9407,7 +9424,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="99" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>59</v>
       </c>
@@ -9466,7 +9483,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="100" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>60</v>
       </c>
@@ -9522,7 +9539,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="101" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>60</v>
       </c>
@@ -9578,7 +9595,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="102" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>60</v>
       </c>
@@ -9634,7 +9651,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="103" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>60</v>
       </c>
@@ -9690,7 +9707,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="104" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>60</v>
       </c>
@@ -9746,7 +9763,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="105" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>60</v>
       </c>
@@ -9802,7 +9819,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="106" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>60</v>
       </c>
@@ -9858,7 +9875,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="107" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>60</v>
       </c>
@@ -9917,7 +9934,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="108" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>60</v>
       </c>
@@ -9970,7 +9987,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="109" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>61</v>
       </c>
@@ -10029,7 +10046,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="110" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>61</v>
       </c>
@@ -10088,7 +10105,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="111" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>61</v>
       </c>
@@ -10147,7 +10164,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="112" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>61</v>
       </c>
@@ -10206,7 +10223,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="113" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>61</v>
       </c>
@@ -10265,7 +10282,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="114" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>61</v>
       </c>
@@ -10324,7 +10341,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="115" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>61</v>
       </c>
@@ -10383,7 +10400,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="116" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>61</v>
       </c>
@@ -10442,7 +10459,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="117" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>61</v>
       </c>
@@ -10501,7 +10518,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="118" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>61</v>
       </c>
@@ -10560,7 +10577,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="119" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>61</v>
       </c>
@@ -10619,7 +10636,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="120" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>61</v>
       </c>
@@ -10678,7 +10695,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="121" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>61</v>
       </c>
@@ -10737,7 +10754,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="122" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>61</v>
       </c>
@@ -10796,7 +10813,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="123" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>61</v>
       </c>
@@ -10855,7 +10872,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="124" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>61</v>
       </c>
@@ -10914,7 +10931,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="125" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>61</v>
       </c>
@@ -10973,7 +10990,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="126" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>61</v>
       </c>
@@ -11032,7 +11049,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="127" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A127">
         <v>61</v>
       </c>
@@ -11085,7 +11102,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="128" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>62</v>
       </c>
@@ -11144,7 +11161,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="129" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A129">
         <v>62</v>
       </c>
@@ -11176,7 +11193,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="130" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>62</v>
       </c>
@@ -11208,7 +11225,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="131" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A131">
         <v>62</v>
       </c>
@@ -11240,7 +11257,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="132" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A132">
         <v>62</v>
       </c>
@@ -11272,7 +11289,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="133" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>62</v>
       </c>
@@ -11304,7 +11321,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="134" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>62</v>
       </c>
@@ -11336,7 +11353,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="135" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A135">
         <v>62</v>
       </c>
@@ -11368,7 +11385,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="136" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A136">
         <v>62</v>
       </c>
@@ -11400,7 +11417,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="137" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A137">
         <v>62</v>
       </c>
@@ -11432,7 +11449,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="138" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>62</v>
       </c>
@@ -11464,7 +11481,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="139" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A139">
         <v>63</v>
       </c>
@@ -11523,7 +11540,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="140" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A140">
         <v>63</v>
       </c>
@@ -11582,7 +11599,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="141" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:26" x14ac:dyDescent="0.3">
       <c r="J141">
         <v>250</v>
       </c>
@@ -11599,7 +11616,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="142" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A142">
         <v>64</v>
       </c>
@@ -11658,7 +11675,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="143" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A143">
         <v>64</v>
       </c>
@@ -11717,7 +11734,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="144" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A144">
         <v>64</v>
       </c>
@@ -11764,7 +11781,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="145" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A145">
         <v>65</v>
       </c>
@@ -11823,7 +11840,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="146" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>65</v>
       </c>
@@ -11882,7 +11899,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="147" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:26" x14ac:dyDescent="0.3">
       <c r="M147">
         <v>40</v>
       </c>
@@ -11896,7 +11913,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="148" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A148">
         <v>66</v>
       </c>
@@ -11955,7 +11972,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="149" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A149">
         <v>66</v>
       </c>
@@ -12014,7 +12031,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="150" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>67</v>
       </c>
@@ -12070,7 +12087,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="151" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A151">
         <v>68</v>
       </c>
@@ -12126,7 +12143,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="152" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A152">
         <v>68</v>
       </c>
@@ -12164,7 +12181,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="153" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A153">
         <v>68</v>
       </c>
@@ -12202,7 +12219,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="154" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A154">
         <v>68</v>
       </c>
@@ -12238,6 +12255,166 @@
       </c>
       <c r="Z154" t="s">
         <v>313</v>
+      </c>
+    </row>
+    <row r="155" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A155">
+        <v>69</v>
+      </c>
+      <c r="B155">
+        <v>69</v>
+      </c>
+      <c r="C155" t="s">
+        <v>465</v>
+      </c>
+      <c r="D155">
+        <v>3</v>
+      </c>
+      <c r="E155" t="s">
+        <v>8</v>
+      </c>
+      <c r="F155" t="s">
+        <v>8</v>
+      </c>
+      <c r="G155" t="s">
+        <v>8</v>
+      </c>
+      <c r="H155" t="s">
+        <v>96</v>
+      </c>
+      <c r="I155" t="s">
+        <v>8</v>
+      </c>
+      <c r="J155" t="s">
+        <v>8</v>
+      </c>
+      <c r="K155" t="s">
+        <v>8</v>
+      </c>
+      <c r="L155" t="s">
+        <v>8</v>
+      </c>
+      <c r="M155" t="s">
+        <v>8</v>
+      </c>
+      <c r="N155" t="s">
+        <v>8</v>
+      </c>
+      <c r="O155" t="s">
+        <v>8</v>
+      </c>
+      <c r="P155" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q155" t="s">
+        <v>8</v>
+      </c>
+      <c r="R155" t="s">
+        <v>8</v>
+      </c>
+      <c r="S155" t="s">
+        <v>8</v>
+      </c>
+      <c r="T155" t="s">
+        <v>8</v>
+      </c>
+      <c r="U155" t="s">
+        <v>8</v>
+      </c>
+      <c r="V155" t="s">
+        <v>8</v>
+      </c>
+      <c r="W155" t="s">
+        <v>8</v>
+      </c>
+      <c r="X155" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y155" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z155" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="156" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A156">
+        <v>69</v>
+      </c>
+      <c r="B156">
+        <v>69</v>
+      </c>
+      <c r="C156" t="s">
+        <v>465</v>
+      </c>
+      <c r="D156" t="s">
+        <v>8</v>
+      </c>
+      <c r="E156" t="s">
+        <v>8</v>
+      </c>
+      <c r="F156" t="s">
+        <v>8</v>
+      </c>
+      <c r="G156" t="s">
+        <v>8</v>
+      </c>
+      <c r="H156" t="s">
+        <v>8</v>
+      </c>
+      <c r="I156" t="s">
+        <v>8</v>
+      </c>
+      <c r="J156" t="s">
+        <v>8</v>
+      </c>
+      <c r="K156" t="s">
+        <v>8</v>
+      </c>
+      <c r="L156" t="s">
+        <v>8</v>
+      </c>
+      <c r="M156" t="s">
+        <v>8</v>
+      </c>
+      <c r="N156" t="s">
+        <v>8</v>
+      </c>
+      <c r="O156" t="s">
+        <v>8</v>
+      </c>
+      <c r="P156" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q156" t="s">
+        <v>8</v>
+      </c>
+      <c r="R156" t="s">
+        <v>8</v>
+      </c>
+      <c r="S156" t="s">
+        <v>8</v>
+      </c>
+      <c r="T156" t="s">
+        <v>8</v>
+      </c>
+      <c r="U156" t="s">
+        <v>8</v>
+      </c>
+      <c r="V156" t="s">
+        <v>8</v>
+      </c>
+      <c r="W156" t="s">
+        <v>8</v>
+      </c>
+      <c r="X156" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y156" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z156" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -12250,38 +12427,38 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
-  <dimension ref="A1:Z50"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:Z52"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="84" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="45.28515625" customWidth="1"/>
-    <col min="7" max="7" width="35.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="45.33203125" customWidth="1"/>
+    <col min="7" max="7" width="35.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.44140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="45" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="45.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="55.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="33.5703125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="38.85546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="44.85546875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="45.28515625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="55.28515625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="53.85546875" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="50.42578125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="34.5703125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="45.44140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="55.44140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="33.5546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="38.88671875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="44.88671875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="45.33203125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="55.33203125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="20.5546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="20.88671875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="53.88671875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="50.44140625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="34.5546875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="27.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>446</v>
       </c>
@@ -12361,7 +12538,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>51</v>
       </c>
@@ -12417,7 +12594,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>51</v>
       </c>
@@ -12473,7 +12650,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>51</v>
       </c>
@@ -12529,7 +12706,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>52</v>
       </c>
@@ -12588,7 +12765,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>52</v>
       </c>
@@ -12647,7 +12824,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>53</v>
       </c>
@@ -12706,7 +12883,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>53</v>
       </c>
@@ -12762,7 +12939,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>53</v>
       </c>
@@ -12833,7 +13010,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>53</v>
       </c>
@@ -12889,7 +13066,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>54</v>
       </c>
@@ -12948,7 +13125,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>54</v>
       </c>
@@ -13022,7 +13199,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>55</v>
       </c>
@@ -13081,7 +13258,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>55</v>
       </c>
@@ -13140,7 +13317,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>55</v>
       </c>
@@ -13196,7 +13373,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>55</v>
       </c>
@@ -13252,7 +13429,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="17" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>55</v>
       </c>
@@ -13308,7 +13485,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="18" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>55</v>
       </c>
@@ -13364,7 +13541,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="19" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>56</v>
       </c>
@@ -13420,7 +13597,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>56</v>
       </c>
@@ -13476,7 +13653,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>56</v>
       </c>
@@ -13532,7 +13709,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>56</v>
       </c>
@@ -13588,7 +13765,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>56</v>
       </c>
@@ -13644,7 +13821,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="24" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>56</v>
       </c>
@@ -13703,7 +13880,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="25" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>56</v>
       </c>
@@ -13759,7 +13936,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>57</v>
       </c>
@@ -13800,7 +13977,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="27" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>58</v>
       </c>
@@ -13847,7 +14024,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="28" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>58</v>
       </c>
@@ -13894,7 +14071,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="29" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>59</v>
       </c>
@@ -13950,7 +14127,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="30" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>60</v>
       </c>
@@ -14006,7 +14183,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="31" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>60</v>
       </c>
@@ -14062,7 +14239,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="32" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>60</v>
       </c>
@@ -14118,7 +14295,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="33" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>61</v>
       </c>
@@ -14174,7 +14351,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="34" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>62</v>
       </c>
@@ -14230,7 +14407,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="35" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>63</v>
       </c>
@@ -14286,7 +14463,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="36" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>63</v>
       </c>
@@ -14342,7 +14519,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="37" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:26" x14ac:dyDescent="0.3">
       <c r="G37">
         <v>250</v>
       </c>
@@ -14353,7 +14530,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="38" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>64</v>
       </c>
@@ -14412,7 +14589,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="39" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>64</v>
       </c>
@@ -14471,7 +14648,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="40" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>64</v>
       </c>
@@ -14530,7 +14707,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="41" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>64</v>
       </c>
@@ -14589,7 +14766,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="42" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>64</v>
       </c>
@@ -14648,7 +14825,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="43" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>64</v>
       </c>
@@ -14707,7 +14884,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="44" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>65</v>
       </c>
@@ -14766,7 +14943,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="45" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>65</v>
       </c>
@@ -14825,7 +15002,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="46" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>66</v>
       </c>
@@ -14881,7 +15058,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="47" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>66</v>
       </c>
@@ -14937,7 +15114,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="48" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>66</v>
       </c>
@@ -14996,7 +15173,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="49" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>67</v>
       </c>
@@ -15037,7 +15214,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="50" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>68</v>
       </c>
@@ -15094,6 +15271,166 @@
       </c>
       <c r="Z50" t="s">
         <v>421</v>
+      </c>
+    </row>
+    <row r="51" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A51">
+        <v>69</v>
+      </c>
+      <c r="B51">
+        <v>69</v>
+      </c>
+      <c r="C51" t="s">
+        <v>18</v>
+      </c>
+      <c r="D51">
+        <v>3</v>
+      </c>
+      <c r="E51" t="s">
+        <v>8</v>
+      </c>
+      <c r="F51" t="s">
+        <v>8</v>
+      </c>
+      <c r="G51" t="s">
+        <v>8</v>
+      </c>
+      <c r="H51" t="s">
+        <v>8</v>
+      </c>
+      <c r="I51" t="s">
+        <v>8</v>
+      </c>
+      <c r="J51" t="s">
+        <v>8</v>
+      </c>
+      <c r="K51" t="s">
+        <v>8</v>
+      </c>
+      <c r="L51" t="s">
+        <v>8</v>
+      </c>
+      <c r="M51" t="s">
+        <v>8</v>
+      </c>
+      <c r="N51" t="s">
+        <v>8</v>
+      </c>
+      <c r="O51" t="s">
+        <v>8</v>
+      </c>
+      <c r="P51" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>8</v>
+      </c>
+      <c r="R51" t="s">
+        <v>8</v>
+      </c>
+      <c r="S51" t="s">
+        <v>8</v>
+      </c>
+      <c r="T51" t="s">
+        <v>8</v>
+      </c>
+      <c r="U51" t="s">
+        <v>8</v>
+      </c>
+      <c r="V51" t="s">
+        <v>8</v>
+      </c>
+      <c r="W51" t="s">
+        <v>8</v>
+      </c>
+      <c r="X51" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y51" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z51" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="52" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A52">
+        <v>69</v>
+      </c>
+      <c r="B52">
+        <v>69</v>
+      </c>
+      <c r="C52" t="s">
+        <v>466</v>
+      </c>
+      <c r="D52" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" t="s">
+        <v>8</v>
+      </c>
+      <c r="F52" t="s">
+        <v>8</v>
+      </c>
+      <c r="G52" t="s">
+        <v>8</v>
+      </c>
+      <c r="H52" t="s">
+        <v>8</v>
+      </c>
+      <c r="I52" t="s">
+        <v>8</v>
+      </c>
+      <c r="J52" t="s">
+        <v>8</v>
+      </c>
+      <c r="K52" t="s">
+        <v>8</v>
+      </c>
+      <c r="L52" t="s">
+        <v>8</v>
+      </c>
+      <c r="M52" t="s">
+        <v>8</v>
+      </c>
+      <c r="N52" t="s">
+        <v>8</v>
+      </c>
+      <c r="O52" t="s">
+        <v>8</v>
+      </c>
+      <c r="P52" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>8</v>
+      </c>
+      <c r="R52" t="s">
+        <v>8</v>
+      </c>
+      <c r="S52" t="s">
+        <v>8</v>
+      </c>
+      <c r="T52" t="s">
+        <v>8</v>
+      </c>
+      <c r="U52" t="s">
+        <v>8</v>
+      </c>
+      <c r="V52" t="s">
+        <v>8</v>
+      </c>
+      <c r="W52" t="s">
+        <v>8</v>
+      </c>
+      <c r="X52" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y52" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z52" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -15106,17 +15443,17 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
-  <dimension ref="A1:E163"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E167"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="150.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="150.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>446</v>
       </c>
@@ -15133,7 +15470,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>51</v>
       </c>
@@ -15150,7 +15487,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>51</v>
       </c>
@@ -15167,7 +15504,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>51</v>
       </c>
@@ -15184,7 +15521,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>51</v>
       </c>
@@ -15201,7 +15538,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>52</v>
       </c>
@@ -15218,7 +15555,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>52</v>
       </c>
@@ -15235,7 +15572,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>52</v>
       </c>
@@ -15252,7 +15589,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>52</v>
       </c>
@@ -15269,7 +15606,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>53</v>
       </c>
@@ -15286,7 +15623,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>53</v>
       </c>
@@ -15303,7 +15640,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>53</v>
       </c>
@@ -15320,7 +15657,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>53</v>
       </c>
@@ -15337,7 +15674,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>53</v>
       </c>
@@ -15354,7 +15691,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>53</v>
       </c>
@@ -15371,7 +15708,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>53</v>
       </c>
@@ -15388,7 +15725,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>53</v>
       </c>
@@ -15405,7 +15742,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>54</v>
       </c>
@@ -15422,7 +15759,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>54</v>
       </c>
@@ -15439,7 +15776,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>54</v>
       </c>
@@ -15456,7 +15793,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>54</v>
       </c>
@@ -15473,7 +15810,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>54</v>
       </c>
@@ -15490,7 +15827,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>54</v>
       </c>
@@ -15507,7 +15844,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>54</v>
       </c>
@@ -15524,7 +15861,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>54</v>
       </c>
@@ -15541,7 +15878,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>55</v>
       </c>
@@ -15558,7 +15895,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>55</v>
       </c>
@@ -15575,7 +15912,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>55</v>
       </c>
@@ -15592,7 +15929,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>55</v>
       </c>
@@ -15609,7 +15946,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>55</v>
       </c>
@@ -15626,7 +15963,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>55</v>
       </c>
@@ -15643,7 +15980,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>55</v>
       </c>
@@ -15660,7 +15997,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>55</v>
       </c>
@@ -15677,7 +16014,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>55</v>
       </c>
@@ -15694,7 +16031,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>55</v>
       </c>
@@ -15711,7 +16048,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>55</v>
       </c>
@@ -15728,7 +16065,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>55</v>
       </c>
@@ -15745,7 +16082,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>55</v>
       </c>
@@ -15762,7 +16099,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>55</v>
       </c>
@@ -15779,7 +16116,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>55</v>
       </c>
@@ -15796,7 +16133,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>55</v>
       </c>
@@ -15813,7 +16150,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>55</v>
       </c>
@@ -15830,7 +16167,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>55</v>
       </c>
@@ -15847,7 +16184,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>55</v>
       </c>
@@ -15864,7 +16201,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>55</v>
       </c>
@@ -15881,7 +16218,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>55</v>
       </c>
@@ -15898,7 +16235,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>55</v>
       </c>
@@ -15915,7 +16252,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>55</v>
       </c>
@@ -15932,7 +16269,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>55</v>
       </c>
@@ -15949,7 +16286,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>55</v>
       </c>
@@ -15966,7 +16303,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>55</v>
       </c>
@@ -15983,7 +16320,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>55</v>
       </c>
@@ -16000,7 +16337,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>55</v>
       </c>
@@ -16017,7 +16354,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>55</v>
       </c>
@@ -16034,7 +16371,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>55</v>
       </c>
@@ -16051,7 +16388,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>55</v>
       </c>
@@ -16068,7 +16405,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>55</v>
       </c>
@@ -16085,7 +16422,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>55</v>
       </c>
@@ -16102,7 +16439,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>55</v>
       </c>
@@ -16119,7 +16456,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>55</v>
       </c>
@@ -16136,7 +16473,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>56</v>
       </c>
@@ -16153,7 +16490,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>56</v>
       </c>
@@ -16170,7 +16507,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>56</v>
       </c>
@@ -16187,7 +16524,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>56</v>
       </c>
@@ -16204,7 +16541,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>56</v>
       </c>
@@ -16221,7 +16558,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>56</v>
       </c>
@@ -16238,7 +16575,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>56</v>
       </c>
@@ -16255,7 +16592,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>56</v>
       </c>
@@ -16272,7 +16609,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>56</v>
       </c>
@@ -16289,7 +16626,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>56</v>
       </c>
@@ -16306,7 +16643,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>56</v>
       </c>
@@ -16323,7 +16660,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>56</v>
       </c>
@@ -16340,7 +16677,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>56</v>
       </c>
@@ -16357,7 +16694,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>56</v>
       </c>
@@ -16374,7 +16711,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>56</v>
       </c>
@@ -16391,7 +16728,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>56</v>
       </c>
@@ -16408,7 +16745,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>56</v>
       </c>
@@ -16425,7 +16762,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>56</v>
       </c>
@@ -16442,7 +16779,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>56</v>
       </c>
@@ -16459,7 +16796,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>56</v>
       </c>
@@ -16476,7 +16813,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>56</v>
       </c>
@@ -16493,7 +16830,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>56</v>
       </c>
@@ -16510,7 +16847,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>56</v>
       </c>
@@ -16527,7 +16864,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>56</v>
       </c>
@@ -16544,7 +16881,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>56</v>
       </c>
@@ -16561,7 +16898,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>56</v>
       </c>
@@ -16578,7 +16915,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>56</v>
       </c>
@@ -16595,7 +16932,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>57</v>
       </c>
@@ -16612,7 +16949,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>57</v>
       </c>
@@ -16629,7 +16966,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>57</v>
       </c>
@@ -16646,7 +16983,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>57</v>
       </c>
@@ -16663,7 +17000,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>57</v>
       </c>
@@ -16680,7 +17017,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>58</v>
       </c>
@@ -16697,7 +17034,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>58</v>
       </c>
@@ -16714,7 +17051,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>58</v>
       </c>
@@ -16731,7 +17068,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>59</v>
       </c>
@@ -16748,7 +17085,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>59</v>
       </c>
@@ -16765,7 +17102,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>59</v>
       </c>
@@ -16782,7 +17119,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>59</v>
       </c>
@@ -16799,7 +17136,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>59</v>
       </c>
@@ -16816,7 +17153,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>59</v>
       </c>
@@ -16833,7 +17170,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>59</v>
       </c>
@@ -16850,7 +17187,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>59</v>
       </c>
@@ -16867,7 +17204,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>59</v>
       </c>
@@ -16884,7 +17221,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>59</v>
       </c>
@@ -16901,7 +17238,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>59</v>
       </c>
@@ -16918,7 +17255,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>59</v>
       </c>
@@ -16935,7 +17272,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>59</v>
       </c>
@@ -16952,7 +17289,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>59</v>
       </c>
@@ -16969,7 +17306,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>59</v>
       </c>
@@ -16986,7 +17323,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>60</v>
       </c>
@@ -17003,7 +17340,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>60</v>
       </c>
@@ -17020,7 +17357,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>60</v>
       </c>
@@ -17037,7 +17374,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>60</v>
       </c>
@@ -17054,7 +17391,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>60</v>
       </c>
@@ -17071,7 +17408,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>60</v>
       </c>
@@ -17088,7 +17425,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>60</v>
       </c>
@@ -17105,7 +17442,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>60</v>
       </c>
@@ -17122,7 +17459,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>60</v>
       </c>
@@ -17139,7 +17476,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>61</v>
       </c>
@@ -17156,7 +17493,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>61</v>
       </c>
@@ -17173,7 +17510,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>61</v>
       </c>
@@ -17190,7 +17527,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>61</v>
       </c>
@@ -17207,7 +17544,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>61</v>
       </c>
@@ -17224,7 +17561,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>61</v>
       </c>
@@ -17241,7 +17578,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>61</v>
       </c>
@@ -17258,7 +17595,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A127">
         <v>61</v>
       </c>
@@ -17275,7 +17612,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>61</v>
       </c>
@@ -17292,7 +17629,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A129">
         <v>61</v>
       </c>
@@ -17309,7 +17646,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>61</v>
       </c>
@@ -17326,7 +17663,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A131">
         <v>61</v>
       </c>
@@ -17343,7 +17680,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A132">
         <v>61</v>
       </c>
@@ -17360,7 +17697,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>61</v>
       </c>
@@ -17377,7 +17714,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>61</v>
       </c>
@@ -17394,7 +17731,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A135">
         <v>61</v>
       </c>
@@ -17411,7 +17748,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A136">
         <v>61</v>
       </c>
@@ -17428,7 +17765,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A137">
         <v>61</v>
       </c>
@@ -17445,7 +17782,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>61</v>
       </c>
@@ -17462,7 +17799,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A139">
         <v>62</v>
       </c>
@@ -17479,7 +17816,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A140">
         <v>62</v>
       </c>
@@ -17496,7 +17833,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A141">
         <v>62</v>
       </c>
@@ -17513,7 +17850,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A142">
         <v>62</v>
       </c>
@@ -17530,7 +17867,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A143">
         <v>62</v>
       </c>
@@ -17547,7 +17884,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A144">
         <v>62</v>
       </c>
@@ -17564,7 +17901,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A145">
         <v>62</v>
       </c>
@@ -17581,7 +17918,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>62</v>
       </c>
@@ -17598,7 +17935,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A147">
         <v>62</v>
       </c>
@@ -17615,7 +17952,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A148">
         <v>62</v>
       </c>
@@ -17632,7 +17969,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A149">
         <v>62</v>
       </c>
@@ -17649,7 +17986,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>63</v>
       </c>
@@ -17666,7 +18003,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A151">
         <v>63</v>
       </c>
@@ -17683,7 +18020,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A152">
         <v>64</v>
       </c>
@@ -17700,7 +18037,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A153">
         <v>64</v>
       </c>
@@ -17717,7 +18054,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A154">
         <v>64</v>
       </c>
@@ -17734,7 +18071,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A155">
         <v>65</v>
       </c>
@@ -17751,7 +18088,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A156">
         <v>65</v>
       </c>
@@ -17768,7 +18105,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A157">
         <v>66</v>
       </c>
@@ -17785,7 +18122,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A158">
         <v>66</v>
       </c>
@@ -17802,7 +18139,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A159">
         <v>67</v>
       </c>
@@ -17819,7 +18156,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A160">
         <v>68</v>
       </c>
@@ -17836,7 +18173,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A161">
         <v>68</v>
       </c>
@@ -17853,7 +18190,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A162">
         <v>68</v>
       </c>
@@ -17870,7 +18207,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A163">
         <v>68</v>
       </c>
@@ -17885,6 +18222,74 @@
       </c>
       <c r="E163" t="s">
         <v>312</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A164">
+        <v>69</v>
+      </c>
+      <c r="B164">
+        <v>69</v>
+      </c>
+      <c r="C164">
+        <v>3</v>
+      </c>
+      <c r="D164" t="s">
+        <v>8</v>
+      </c>
+      <c r="E164" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A165">
+        <v>69</v>
+      </c>
+      <c r="B165">
+        <v>69</v>
+      </c>
+      <c r="C165">
+        <v>3</v>
+      </c>
+      <c r="D165" t="s">
+        <v>8</v>
+      </c>
+      <c r="E165" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A166">
+        <v>69</v>
+      </c>
+      <c r="B166">
+        <v>69</v>
+      </c>
+      <c r="C166">
+        <v>3</v>
+      </c>
+      <c r="D166" t="s">
+        <v>8</v>
+      </c>
+      <c r="E166" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A167">
+        <v>69</v>
+      </c>
+      <c r="B167">
+        <v>69</v>
+      </c>
+      <c r="C167" t="s">
+        <v>8</v>
+      </c>
+      <c r="D167" t="s">
+        <v>8</v>
+      </c>
+      <c r="E167" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -17897,17 +18302,17 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
-  <dimension ref="A1:E53"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E55"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="39.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="39.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>446</v>
       </c>
@@ -17924,7 +18329,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>51</v>
       </c>
@@ -17941,7 +18346,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>51</v>
       </c>
@@ -17958,7 +18363,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>51</v>
       </c>
@@ -17975,7 +18380,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>52</v>
       </c>
@@ -17992,7 +18397,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>52</v>
       </c>
@@ -18009,7 +18414,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>53</v>
       </c>
@@ -18026,7 +18431,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>53</v>
       </c>
@@ -18043,7 +18448,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>53</v>
       </c>
@@ -18060,7 +18465,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>53</v>
       </c>
@@ -18077,7 +18482,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>54</v>
       </c>
@@ -18094,7 +18499,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>54</v>
       </c>
@@ -18111,7 +18516,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>54</v>
       </c>
@@ -18128,7 +18533,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>55</v>
       </c>
@@ -18145,7 +18550,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>55</v>
       </c>
@@ -18162,7 +18567,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>55</v>
       </c>
@@ -18179,7 +18584,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>55</v>
       </c>
@@ -18196,7 +18601,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>55</v>
       </c>
@@ -18213,7 +18618,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>55</v>
       </c>
@@ -18230,7 +18635,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>56</v>
       </c>
@@ -18247,7 +18652,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>56</v>
       </c>
@@ -18264,7 +18669,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>56</v>
       </c>
@@ -18281,7 +18686,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>56</v>
       </c>
@@ -18298,7 +18703,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>56</v>
       </c>
@@ -18315,7 +18720,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>56</v>
       </c>
@@ -18332,7 +18737,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>56</v>
       </c>
@@ -18349,7 +18754,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>57</v>
       </c>
@@ -18366,7 +18771,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>58</v>
       </c>
@@ -18383,7 +18788,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>58</v>
       </c>
@@ -18400,7 +18805,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>59</v>
       </c>
@@ -18417,7 +18822,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>60</v>
       </c>
@@ -18434,7 +18839,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>60</v>
       </c>
@@ -18451,7 +18856,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>60</v>
       </c>
@@ -18468,7 +18873,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>61</v>
       </c>
@@ -18485,7 +18890,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>62</v>
       </c>
@@ -18502,7 +18907,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>63</v>
       </c>
@@ -18519,7 +18924,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>63</v>
       </c>
@@ -18536,7 +18941,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>64</v>
       </c>
@@ -18553,7 +18958,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>64</v>
       </c>
@@ -18570,7 +18975,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>64</v>
       </c>
@@ -18587,7 +18992,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>64</v>
       </c>
@@ -18604,7 +19009,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>64</v>
       </c>
@@ -18621,7 +19026,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>64</v>
       </c>
@@ -18638,7 +19043,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>65</v>
       </c>
@@ -18655,7 +19060,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>65</v>
       </c>
@@ -18672,7 +19077,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>66</v>
       </c>
@@ -18689,7 +19094,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>66</v>
       </c>
@@ -18706,7 +19111,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>66</v>
       </c>
@@ -18723,7 +19128,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>67</v>
       </c>
@@ -18740,7 +19145,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>67</v>
       </c>
@@ -18757,7 +19162,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>67</v>
       </c>
@@ -18774,7 +19179,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>67</v>
       </c>
@@ -18791,7 +19196,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>68</v>
       </c>
@@ -18806,6 +19211,40 @@
       </c>
       <c r="E53" t="s">
         <v>418</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A54">
+        <v>69</v>
+      </c>
+      <c r="B54">
+        <v>69</v>
+      </c>
+      <c r="C54">
+        <v>3</v>
+      </c>
+      <c r="D54" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A55">
+        <v>69</v>
+      </c>
+      <c r="B55">
+        <v>69</v>
+      </c>
+      <c r="C55" t="s">
+        <v>8</v>
+      </c>
+      <c r="D55" t="s">
+        <v>8</v>
+      </c>
+      <c r="E55" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
